--- a/20260319行事参加者確認一覧.xlsx
+++ b/20260319行事参加者確認一覧.xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -176,10 +176,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¸ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂºÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -16948,6 +16948,9 @@
       <c r="C5" t="str">
         <v>蔭山和那</v>
       </c>
+      <c r="D5" t="str">
+        <v>〇</v>
+      </c>
       <c r="F5" t="str">
         <v>〇</v>
       </c>
